--- a/companies/databricks/financials/databricks_model_2026-08-13.xlsx
+++ b/companies/databricks/financials/databricks_model_2026-08-13.xlsx
@@ -228,10 +228,10 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -445,7 +445,7 @@
       <text>
         <t>ASSUMPTION
 Exit multiple
-Basis: Applied to terminal-year revenue in the exit-multiple method.</t>
+Basis: Applied to terminal-year revenue. A company growing at the terminal rate is a mature business, so this is deliberately well below what the company commands today as a high-growth private.</t>
       </text>
     </comment>
     <comment ref="D31" authorId="0" shapeId="0">
@@ -501,6 +501,13 @@
         <t>Back-solved from the latest stored annualised revenue and the stored growth ladder. An estimate, not a disclosed figure.</t>
       </text>
     </comment>
+    <comment ref="D23" authorId="0" shapeId="0">
+      <text>
+        <t>ASSUMPTION
+Capex and working capital
+Basis: software businesses are asset-light; 4% of revenue covers capitalised development and working capital swings. Raise it for anyone building their own data centres.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -511,7 +518,12 @@
     <author>HRPB Desk</author>
   </authors>
   <commentList>
-    <comment ref="D22" authorId="0" shapeId="0">
+    <comment ref="D14" authorId="0" shapeId="0">
+      <text>
+        <t>When the two methods disagree by more than about 1.5x, averaging them hides the disagreement rather than resolving it. Use the perpetuity figure and treat the multiple as a cross-check.</t>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="0" shapeId="0">
       <text>
         <t>Equity only. Debt informs risk, never this ratio (house ruling R1).</t>
       </text>
@@ -809,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E32"/>
+  <dimension ref="B2:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -959,101 +971,123 @@
         </is>
       </c>
       <c r="D17" s="9">
-        <f>IF(Valuation!$D$16&lt;=0,1,0)</f>
+        <f>IF(Valuation!$D$17&lt;=0,1,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Terminal methods disagree by more than 1.5x?</t>
+        </is>
+      </c>
+      <c r="D18" s="9">
+        <f>IF(Valuation!$D$14&gt;1.5,1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Terminal value more than 75% of enterprise value?</t>
+        </is>
+      </c>
+      <c r="D19" s="9">
+        <f>IF(Valuation!$D$17=0,0,IF(D15/Valuation!$D$17&gt;0.75,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>All checks should read No.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>How much of this model is fact</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Inputs drawn from sourced facts</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Inputs that are desk assumptions</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>12</v>
-      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
+          <t>Inputs drawn from sourced facts</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Inputs that are desk assumptions</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>Share sourced</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.3684210526315789</v>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="B24" s="13" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE ONLY — most inputs are desk assumptions. This company discloses too little to support a decision model. Treat the outputs as a shape, not a number.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="14" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Convention</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="15" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>Blue text — an input you may change</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="16" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="16" t="inlineStr">
         <is>
           <t>Yellow fill — an assumption, not a sourced fact</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="17" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Black text — a formula; do not overwrite</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="18" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
         <is>
           <t>Green text — a link to another sheet</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Every blue cell carries a note with its source and date. Hover to read it.</t>
         </is>
@@ -1378,7 +1412,7 @@
         </is>
       </c>
       <c r="D30" s="27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -3197,7 +3231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N27"/>
+  <dimension ref="B2:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3875,170 +3909,180 @@
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
+          <t>Capital expenditure and working capital (% of revenue)</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
           <t>Capital expenditure and working capital</t>
         </is>
       </c>
-      <c r="D23" s="33">
-        <f>-D9*0.06</f>
-        <v/>
-      </c>
-      <c r="E23" s="33">
-        <f>-E9*0.06</f>
-        <v/>
-      </c>
-      <c r="F23" s="33">
-        <f>-F9*0.06</f>
-        <v/>
-      </c>
-      <c r="G23" s="33">
-        <f>-G9*0.06</f>
-        <v/>
-      </c>
-      <c r="H23" s="33">
-        <f>-H9*0.06</f>
-        <v/>
-      </c>
-      <c r="I23" s="33">
-        <f>-I9*0.06</f>
-        <v/>
-      </c>
-      <c r="J23" s="33">
-        <f>-J9*0.06</f>
-        <v/>
-      </c>
-      <c r="K23" s="33">
-        <f>-K9*0.06</f>
-        <v/>
-      </c>
-      <c r="L23" s="33">
-        <f>-L9*0.06</f>
-        <v/>
-      </c>
-      <c r="M23" s="33">
-        <f>-M9*0.06</f>
-        <v/>
-      </c>
-      <c r="N23" s="33">
-        <f>-N9*0.06</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
+      <c r="D24" s="33">
+        <f>-D9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="E24" s="33">
+        <f>-E9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="F24" s="33">
+        <f>-F9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>-G9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="H24" s="33">
+        <f>-H9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="I24" s="33">
+        <f>-I9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="J24" s="33">
+        <f>-J9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="K24" s="33">
+        <f>-K9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="L24" s="33">
+        <f>-L9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="M24" s="33">
+        <f>-M9*Model!$D$23</f>
+        <v/>
+      </c>
+      <c r="N24" s="33">
+        <f>-N9*Model!$D$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="D24" s="34">
-        <f>D18+D22+D23</f>
-        <v/>
-      </c>
-      <c r="E24" s="34">
-        <f>E18+E22+E23</f>
-        <v/>
-      </c>
-      <c r="F24" s="34">
-        <f>F18+F22+F23</f>
-        <v/>
-      </c>
-      <c r="G24" s="34">
-        <f>G18+G22+G23</f>
-        <v/>
-      </c>
-      <c r="H24" s="34">
-        <f>H18+H22+H23</f>
-        <v/>
-      </c>
-      <c r="I24" s="34">
-        <f>I18+I22+I23</f>
-        <v/>
-      </c>
-      <c r="J24" s="34">
-        <f>J18+J22+J23</f>
-        <v/>
-      </c>
-      <c r="K24" s="34">
-        <f>K18+K22+K23</f>
-        <v/>
-      </c>
-      <c r="L24" s="34">
-        <f>L18+L22+L23</f>
-        <v/>
-      </c>
-      <c r="M24" s="34">
-        <f>M18+M22+M23</f>
-        <v/>
-      </c>
-      <c r="N24" s="34">
-        <f>N18+N22+N23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="D25" s="34">
+        <f>D18+D22+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="34">
+        <f>E18+E22+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="34">
+        <f>F18+F22+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>G18+G22+G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>H18+H22+H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="34">
+        <f>I18+I22+I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="34">
+        <f>J18+J22+J24</f>
+        <v/>
+      </c>
+      <c r="K25" s="34">
+        <f>K18+K22+K24</f>
+        <v/>
+      </c>
+      <c r="L25" s="34">
+        <f>L18+L22+L24</f>
+        <v/>
+      </c>
+      <c r="M25" s="34">
+        <f>M18+M22+M24</f>
+        <v/>
+      </c>
+      <c r="N25" s="34">
+        <f>N18+N22+N24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Per-employee and efficiency</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Revenue per employee ($000)</t>
         </is>
       </c>
-      <c r="D27" s="33">
+      <c r="D28" s="33">
         <f>IF(D9=0,0,D9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="E27" s="33">
+      <c r="E28" s="33">
         <f>IF(E9=0,0,E9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="F27" s="33">
+      <c r="F28" s="33">
         <f>IF(F9=0,0,F9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="G27" s="33">
+      <c r="G28" s="33">
         <f>IF(G9=0,0,G9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="H27" s="33">
+      <c r="H28" s="33">
         <f>IF(H9=0,0,H9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="I27" s="33">
+      <c r="I28" s="33">
         <f>IF(I9=0,0,I9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="J27" s="33">
+      <c r="J28" s="33">
         <f>IF(J9=0,0,J9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="K27" s="33">
+      <c r="K28" s="33">
         <f>IF(K9=0,0,K9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="L27" s="33">
+      <c r="L28" s="33">
         <f>IF(L9=0,0,L9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="M27" s="33">
+      <c r="M28" s="33">
         <f>IF(M9=0,0,M9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
-      <c r="N27" s="33">
+      <c r="N28" s="33">
         <f>IF(N9=0,0,N9*1000/MAX(1,Inputs!$D$34))</f>
         <v/>
       </c>
@@ -4055,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N22"/>
+  <dimension ref="B2:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4209,27 +4253,27 @@
         <v>0</v>
       </c>
       <c r="I9" s="33">
-        <f>Model!I24*I8</f>
+        <f>Model!I25*I8</f>
         <v/>
       </c>
       <c r="J9" s="33">
-        <f>Model!J24*J8</f>
+        <f>Model!J25*J8</f>
         <v/>
       </c>
       <c r="K9" s="33">
-        <f>Model!K24*K8</f>
+        <f>Model!K25*K8</f>
         <v/>
       </c>
       <c r="L9" s="33">
-        <f>Model!L24*L8</f>
+        <f>Model!L25*L8</f>
         <v/>
       </c>
       <c r="M9" s="33">
-        <f>Model!M24*M8</f>
+        <f>Model!M25*M8</f>
         <v/>
       </c>
       <c r="N9" s="33">
-        <f>Model!N24*N8</f>
+        <f>Model!N25*N8</f>
         <v/>
       </c>
     </row>
@@ -4251,7 +4295,7 @@
         </is>
       </c>
       <c r="D12" s="33">
-        <f>Model!N24*(1+Inputs!$D$14)/(Inputs!$D$28-Inputs!$D$14)*N8</f>
+        <f>Model!N25*(1+Inputs!$D$14)/(Inputs!$D$28-Inputs!$D$14)*N8</f>
         <v/>
       </c>
     </row>
@@ -4269,84 +4313,95 @@
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Terminal value used (average of the two)</t>
-        </is>
-      </c>
-      <c r="D14" s="33">
-        <f>AVERAGE(D12,D13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="36" t="inlineStr">
+          <t>Spread between the two methods</t>
+        </is>
+      </c>
+      <c r="D14" s="36">
+        <f>IF(MIN(D12,D13)=0,0,MAX(D12,D13)/MIN(D12,D13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Terminal value used (perpetuity; multiple is the cross-check)</t>
+        </is>
+      </c>
+      <c r="D15" s="34">
+        <f>D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="D16" s="37">
-        <f>D11+D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="D17" s="38">
+        <f>D11+D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cross-checks against the stored mark</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Latest stored valuation</t>
-        </is>
-      </c>
-      <c r="D19" s="38">
-        <f>Inputs!$D$26</f>
-        <v/>
-      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Model value against the stored mark</t>
+          <t>Latest stored valuation</t>
         </is>
       </c>
       <c r="D20" s="39">
-        <f>IF(D19=0,0,Valuation!$D$16/D19)</f>
+        <f>Inputs!$D$26</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Stored mark against latest revenue</t>
-        </is>
-      </c>
-      <c r="D21" s="39">
-        <f>IF(Model!H9=0,0,D19/Model!H9)</f>
+          <t>Model value against the stored mark</t>
+        </is>
+      </c>
+      <c r="D21" s="36">
+        <f>IF(D20=0,0,Valuation!$D$17/D20)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="8" t="inlineStr">
         <is>
+          <t>Stored mark against latest revenue</t>
+        </is>
+      </c>
+      <c r="D22" s="36">
+        <f>IF(Model!H9=0,0,D20/Model!H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>Stored mark per dollar of equity raised</t>
         </is>
       </c>
-      <c r="D22" s="39">
-        <f>IF(Inputs!$D$27=0,0,D19/Inputs!$D$27)</f>
+      <c r="D23" s="36">
+        <f>IF(Inputs!$D$27=0,0,D20/Inputs!$D$27)</f>
         <v/>
       </c>
     </row>
@@ -4436,47 +4491,47 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="39">
         <f>Model!D9</f>
         <v/>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="39">
         <f>Model!E9</f>
         <v/>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="39">
         <f>Model!F9</f>
         <v/>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="39">
         <f>Model!G9</f>
         <v/>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="39">
         <f>Model!H9</f>
         <v/>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="39">
         <f>Model!I9</f>
         <v/>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="39">
         <f>Model!J9</f>
         <v/>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="39">
         <f>Model!K9</f>
         <v/>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="39">
         <f>Model!L9</f>
         <v/>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="39">
         <f>Model!M9</f>
         <v/>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="39">
         <f>Model!N9</f>
         <v/>
       </c>
@@ -4487,47 +4542,47 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="39">
         <f>Model!D13</f>
         <v/>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="39">
         <f>Model!E13</f>
         <v/>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="39">
         <f>Model!F13</f>
         <v/>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="39">
         <f>Model!G13</f>
         <v/>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="39">
         <f>Model!H13</f>
         <v/>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="39">
         <f>Model!I13</f>
         <v/>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="39">
         <f>Model!J13</f>
         <v/>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="39">
         <f>Model!K13</f>
         <v/>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="39">
         <f>Model!L13</f>
         <v/>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="39">
         <f>Model!M13</f>
         <v/>
       </c>
-      <c r="N8" s="38">
+      <c r="N8" s="39">
         <f>Model!N13</f>
         <v/>
       </c>
@@ -4538,47 +4593,47 @@
           <t>Operating profit</t>
         </is>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="39">
         <f>Model!D18</f>
         <v/>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="39">
         <f>Model!E18</f>
         <v/>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="39">
         <f>Model!F18</f>
         <v/>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="39">
         <f>Model!G18</f>
         <v/>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="39">
         <f>Model!H18</f>
         <v/>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="39">
         <f>Model!I18</f>
         <v/>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="39">
         <f>Model!J18</f>
         <v/>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="39">
         <f>Model!K18</f>
         <v/>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="39">
         <f>Model!L18</f>
         <v/>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="39">
         <f>Model!M18</f>
         <v/>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="39">
         <f>Model!N18</f>
         <v/>
       </c>
@@ -4589,59 +4644,59 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="D10" s="38">
-        <f>Model!D24</f>
-        <v/>
-      </c>
-      <c r="E10" s="38">
-        <f>Model!E24</f>
-        <v/>
-      </c>
-      <c r="F10" s="38">
-        <f>Model!F24</f>
-        <v/>
-      </c>
-      <c r="G10" s="38">
-        <f>Model!G24</f>
-        <v/>
-      </c>
-      <c r="H10" s="38">
-        <f>Model!H24</f>
-        <v/>
-      </c>
-      <c r="I10" s="38">
-        <f>Model!I24</f>
-        <v/>
-      </c>
-      <c r="J10" s="38">
-        <f>Model!J24</f>
-        <v/>
-      </c>
-      <c r="K10" s="38">
-        <f>Model!K24</f>
-        <v/>
-      </c>
-      <c r="L10" s="38">
-        <f>Model!L24</f>
-        <v/>
-      </c>
-      <c r="M10" s="38">
-        <f>Model!M24</f>
-        <v/>
-      </c>
-      <c r="N10" s="38">
-        <f>Model!N24</f>
+      <c r="D10" s="39">
+        <f>Model!D25</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
+        <f>Model!E25</f>
+        <v/>
+      </c>
+      <c r="F10" s="39">
+        <f>Model!F25</f>
+        <v/>
+      </c>
+      <c r="G10" s="39">
+        <f>Model!G25</f>
+        <v/>
+      </c>
+      <c r="H10" s="39">
+        <f>Model!H25</f>
+        <v/>
+      </c>
+      <c r="I10" s="39">
+        <f>Model!I25</f>
+        <v/>
+      </c>
+      <c r="J10" s="39">
+        <f>Model!J25</f>
+        <v/>
+      </c>
+      <c r="K10" s="39">
+        <f>Model!K25</f>
+        <v/>
+      </c>
+      <c r="L10" s="39">
+        <f>Model!L25</f>
+        <v/>
+      </c>
+      <c r="M10" s="39">
+        <f>Model!M25</f>
+        <v/>
+      </c>
+      <c r="N10" s="39">
+        <f>Model!N25</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Enterprise value (discounted cash flow)</t>
         </is>
       </c>
-      <c r="D12" s="37">
-        <f>Valuation!$D$16</f>
+      <c r="D12" s="38">
+        <f>Valuation!$D$17</f>
         <v/>
       </c>
     </row>
